--- a/data/trans_orig/P6704-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P6704-Estudios-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si le cuesta olvidar los problemas del trabajo en 2012</t>
+          <t>Población según si le cuesta olvidar los problemas del trabajo en 2012 (tasa de respuesta: 99,01%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>27758</t>
+          <t>29132</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>50855</t>
+          <t>51646</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>40690</t>
+          <t>40132</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>63551</t>
+          <t>64567</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>28,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>45,75%</t>
+          <t>46,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>75672</t>
+          <t>74227</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>106325</t>
+          <t>107278</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>33,22%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27869</t>
+          <t>27140</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>50131</t>
+          <t>48639</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17649</t>
+          <t>17880</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>36861</t>
+          <t>37285</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>51103</t>
+          <t>51217</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>81904</t>
+          <t>80475</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>24,92%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>43458</t>
+          <t>44704</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>69506</t>
+          <t>71821</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>37,77%</t>
+          <t>39,03%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>25192</t>
+          <t>24141</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>46152</t>
+          <t>44734</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>32,2%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>74639</t>
+          <t>73446</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>107475</t>
+          <t>106914</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>33,11%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12863</t>
+          <t>12791</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31165</t>
+          <t>30764</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3020</t>
+          <t>3104</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14716</t>
+          <t>14474</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>19458</t>
+          <t>19368</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>40590</t>
+          <t>40781</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,63%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>20990</t>
+          <t>21393</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>40922</t>
+          <t>41375</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>12452</t>
+          <t>12062</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>28833</t>
+          <t>29486</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>37893</t>
+          <t>37963</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>63981</t>
+          <t>64745</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>20,05%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>162046</t>
+          <t>160468</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>212616</t>
+          <t>211675</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>111932</t>
+          <t>111347</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>151903</t>
+          <t>152418</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>287003</t>
+          <t>284668</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>353650</t>
+          <t>349662</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>23,59%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>130153</t>
+          <t>128485</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>176763</t>
+          <t>178291</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>84287</t>
+          <t>85648</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>122693</t>
+          <t>124706</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>225713</t>
+          <t>228161</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>286373</t>
+          <t>288228</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,45%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>252118</t>
+          <t>253371</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>308755</t>
+          <t>310425</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>137399</t>
+          <t>137721</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>181868</t>
+          <t>182350</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>32,01%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>406398</t>
+          <t>406608</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>478158</t>
+          <t>475716</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>32,1%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>133449</t>
+          <t>132223</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>179552</t>
+          <t>180487</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>82253</t>
+          <t>78675</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>118651</t>
+          <t>114856</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>224822</t>
+          <t>224093</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>282321</t>
+          <t>284259</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>19,18%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>116390</t>
+          <t>114944</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>163892</t>
+          <t>159184</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>62832</t>
+          <t>60669</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>95986</t>
+          <t>95880</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>186533</t>
+          <t>188701</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>242128</t>
+          <t>245426</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,56%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>28436</t>
+          <t>29349</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>54432</t>
+          <t>53773</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>28794</t>
+          <t>29506</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>54017</t>
+          <t>53206</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>64605</t>
+          <t>61944</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>99654</t>
+          <t>99631</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>53084</t>
+          <t>52793</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>83766</t>
+          <t>88954</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>21208</t>
+          <t>22589</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>44581</t>
+          <t>45554</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>83288</t>
+          <t>83035</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>122521</t>
+          <t>120681</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,02%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>84276</t>
+          <t>85088</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>119711</t>
+          <t>118614</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>37,98%</t>
+          <t>37,63%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>63587</t>
+          <t>63417</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>95725</t>
+          <t>95545</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>41,1%</t>
+          <t>41,02%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>158314</t>
+          <t>158968</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>204432</t>
+          <t>204126</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>37,29%</t>
+          <t>37,24%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>39983</t>
+          <t>39307</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>65303</t>
+          <t>66776</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>34164</t>
+          <t>33614</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>59456</t>
+          <t>60073</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>78796</t>
+          <t>76425</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>116634</t>
+          <t>115504</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,07%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>41542</t>
+          <t>42302</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>71954</t>
+          <t>71340</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>25068</t>
+          <t>23976</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>49365</t>
+          <t>48087</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>73267</t>
+          <t>72346</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>111596</t>
+          <t>109516</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>19,98%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>232110</t>
+          <t>234609</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>293883</t>
+          <t>296220</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>195937</t>
+          <t>193392</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>251279</t>
+          <t>249772</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>446998</t>
+          <t>444716</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>529870</t>
+          <t>527364</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,41%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>228349</t>
+          <t>229723</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>287420</t>
+          <t>289062</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>139152</t>
+          <t>139114</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>185648</t>
+          <t>188696</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>383792</t>
+          <t>383966</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>461390</t>
+          <t>458496</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,48%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>403374</t>
+          <t>405735</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>473528</t>
+          <t>475521</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>28,74%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>33,68%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>243641</t>
+          <t>244209</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>299881</t>
+          <t>304854</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>32,38%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>663053</t>
+          <t>667577</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>756727</t>
+          <t>755178</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>32,16%</t>
+          <t>32,09%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>198839</t>
+          <t>201774</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>254591</t>
+          <t>257875</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>128954</t>
+          <t>126849</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>174063</t>
+          <t>175628</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>344217</t>
+          <t>343964</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>413675</t>
+          <t>418897</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,8%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>194495</t>
+          <t>194241</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>252643</t>
+          <t>250960</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>111350</t>
+          <t>110859</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>155978</t>
+          <t>153483</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>323905</t>
+          <t>318779</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>397335</t>
+          <t>394345</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>16,76%</t>
         </is>
       </c>
     </row>
@@ -3496,7 +3496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si le cuesta olvidar los problemas del trabajo en 2016</t>
+          <t>Población según si le cuesta olvidar los problemas del trabajo en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>25925</t>
+          <t>26641</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>46847</t>
+          <t>47572</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12135</t>
+          <t>12069</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26432</t>
+          <t>26688</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>36,67%</t>
+          <t>37,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>43542</t>
+          <t>43593</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>69728</t>
+          <t>67567</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>31,4%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17647</t>
+          <t>18125</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>36875</t>
+          <t>36507</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8139</t>
+          <t>8331</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21563</t>
+          <t>22258</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>29041</t>
+          <t>29228</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>52970</t>
+          <t>52585</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,43%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>38851</t>
+          <t>39221</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>62788</t>
+          <t>62928</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>27,4%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>43,87%</t>
+          <t>43,97%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>15664</t>
+          <t>15170</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>31444</t>
+          <t>29865</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>43,62%</t>
+          <t>41,43%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>58334</t>
+          <t>59972</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>85911</t>
+          <t>86354</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>27,87%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>39,92%</t>
+          <t>40,13%</t>
         </is>
       </c>
     </row>
@@ -4030,12 +4030,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12432</t>
+          <t>11969</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29945</t>
+          <t>28714</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4045,12 +4045,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3973</t>
+          <t>4059</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14946</t>
+          <t>16124</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>20079</t>
+          <t>20547</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>40724</t>
+          <t>40406</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4115,12 +4115,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>18,78%</t>
         </is>
       </c>
     </row>
@@ -4143,12 +4143,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4995</t>
+          <t>4972</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>17552</t>
+          <t>17750</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4158,12 +4158,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3772</t>
+          <t>3806</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>14667</t>
+          <t>14296</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>11162</t>
+          <t>11713</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>27906</t>
+          <t>27629</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>12,84%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>194847</t>
+          <t>196707</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>250589</t>
+          <t>249231</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>141076</t>
+          <t>141936</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>183971</t>
+          <t>186075</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>28,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>352886</t>
+          <t>352189</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>418908</t>
+          <t>421681</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>26,72%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>126636</t>
+          <t>124389</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>171667</t>
+          <t>169356</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>108163</t>
+          <t>105957</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>146899</t>
+          <t>147660</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>245003</t>
+          <t>243388</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>307138</t>
+          <t>306204</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,4%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>250102</t>
+          <t>248934</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>308336</t>
+          <t>308372</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4614,7 +4614,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>167914</t>
+          <t>170810</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>213881</t>
+          <t>215219</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>32,97%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>432295</t>
+          <t>431216</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>500927</t>
+          <t>506460</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>32,1%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>154918</t>
+          <t>157890</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>205202</t>
+          <t>207090</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>98410</t>
+          <t>96814</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>137202</t>
+          <t>137290</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>264667</t>
+          <t>264728</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>326035</t>
+          <t>324165</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,54%</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>81264</t>
+          <t>82362</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>121213</t>
+          <t>120603</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>42783</t>
+          <t>43298</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>71552</t>
+          <t>72079</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>131722</t>
+          <t>132930</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>179603</t>
+          <t>182287</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,55%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>56710</t>
+          <t>56982</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>87517</t>
+          <t>87679</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>62220</t>
+          <t>62506</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>94555</t>
+          <t>95115</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>128340</t>
+          <t>128015</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>173196</t>
+          <t>171776</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>26,06%</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>56403</t>
+          <t>55575</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>86093</t>
+          <t>88570</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>40988</t>
+          <t>40513</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>68520</t>
+          <t>67960</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>105797</t>
+          <t>104787</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>145891</t>
+          <t>146012</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>22,15%</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>82367</t>
+          <t>83109</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>118828</t>
+          <t>116773</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>33,31%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>71580</t>
+          <t>71216</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>102040</t>
+          <t>103246</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>33,47%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>162166</t>
+          <t>163048</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>209503</t>
+          <t>209238</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>31,75%</t>
         </is>
       </c>
     </row>
@@ -5394,12 +5394,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>47687</t>
+          <t>44912</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>76030</t>
+          <t>75417</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5409,12 +5409,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5429,12 +5429,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>40325</t>
+          <t>41098</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>68075</t>
+          <t>68331</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5444,12 +5444,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>94330</t>
+          <t>94766</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>132108</t>
+          <t>133794</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>20,3%</t>
         </is>
       </c>
     </row>
@@ -5507,12 +5507,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>37908</t>
+          <t>37390</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>65738</t>
+          <t>65502</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5522,12 +5522,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>26137</t>
+          <t>25771</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>48356</t>
+          <t>49600</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>67747</t>
+          <t>68886</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>103399</t>
+          <t>104122</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,8%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>298338</t>
+          <t>300564</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>361798</t>
+          <t>367538</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>235388</t>
+          <t>234327</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>291034</t>
+          <t>289287</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>28,0%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>546350</t>
+          <t>547694</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>632348</t>
+          <t>634772</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>25,89%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>213145</t>
+          <t>218756</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>273492</t>
+          <t>278340</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>171078</t>
+          <t>171019</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>222238</t>
+          <t>220399</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>398757</t>
+          <t>401715</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>479019</t>
+          <t>482287</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,67%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>386203</t>
+          <t>388942</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>460023</t>
+          <t>461917</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>271625</t>
+          <t>270956</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>331427</t>
+          <t>326793</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>31,63%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>678046</t>
+          <t>679753</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>765643</t>
+          <t>771225</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>31,45%</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>231218</t>
+          <t>231663</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>290598</t>
+          <t>288299</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6091,12 +6091,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>155215</t>
+          <t>155421</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>205878</t>
+          <t>204384</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>399603</t>
+          <t>398783</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>476564</t>
+          <t>479309</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,55%</t>
         </is>
       </c>
     </row>
@@ -6189,12 +6189,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>137521</t>
+          <t>137661</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>186560</t>
+          <t>185950</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6204,12 +6204,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>82966</t>
+          <t>81568</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>120525</t>
+          <t>120170</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>231664</t>
+          <t>228942</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>292708</t>
+          <t>292972</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,95%</t>
         </is>
       </c>
     </row>
@@ -6455,7 +6455,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si le cuesta olvidar los problemas del trabajo en 2023</t>
+          <t>Población según si le cuesta olvidar los problemas del trabajo en 2023 (tasa de respuesta: 99,45%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6650,12 +6650,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3863</t>
+          <t>3500</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14442</t>
+          <t>13712</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6665,12 +6665,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>43,84%</t>
+          <t>41,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6685,12 +6685,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2638</t>
+          <t>2375</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8823</t>
+          <t>8558</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>48,47%</t>
+          <t>47,01%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7901</t>
+          <t>7985</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19058</t>
+          <t>20372</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,26%</t>
+          <t>39,83%</t>
         </is>
       </c>
     </row>
@@ -6763,12 +6763,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6772</t>
+          <t>7259</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19611</t>
+          <t>19673</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6778,12 +6778,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>59,53%</t>
+          <t>59,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6798,12 +6798,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1843</t>
+          <t>1814</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7658</t>
+          <t>7799</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6813,12 +6813,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>42,07%</t>
+          <t>42,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10726</t>
+          <t>10665</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>24904</t>
+          <t>24307</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>48,69%</t>
+          <t>47,53%</t>
         </is>
       </c>
     </row>
@@ -6876,12 +6876,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1840</t>
+          <t>1889</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10059</t>
+          <t>10520</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6891,12 +6891,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>31,94%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3550</t>
+          <t>3495</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9651</t>
+          <t>9516</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6926,12 +6926,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>53,02%</t>
+          <t>52,27%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6566</t>
+          <t>6698</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>16653</t>
+          <t>17137</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>33,51%</t>
         </is>
       </c>
     </row>
@@ -6989,12 +6989,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1029</t>
+          <t>1124</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10920</t>
+          <t>11228</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7004,12 +7004,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>34,08%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>603</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4773</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7039,12 +7039,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2496</t>
+          <t>2736</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13822</t>
+          <t>13089</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7074,12 +7074,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>25,59%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>706</t>
+          <t>703</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7663</t>
+          <t>8534</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>25,91%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7142,7 +7142,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3469</t>
+          <t>2902</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7157,7 +7157,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1116</t>
+          <t>739</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>8590</t>
+          <t>8072</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>15,78%</t>
         </is>
       </c>
     </row>
@@ -7332,12 +7332,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>178276</t>
+          <t>177970</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>458082</t>
+          <t>464485</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7347,12 +7347,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>34,84%</t>
+          <t>34,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>89,53%</t>
+          <t>90,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>68759</t>
+          <t>69769</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>96203</t>
+          <t>97113</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7382,12 +7382,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>30,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>42,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>256088</t>
+          <t>255809</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>606797</t>
+          <t>601979</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>34,52%</t>
+          <t>34,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>81,79%</t>
+          <t>81,14%</t>
         </is>
       </c>
     </row>
@@ -7445,12 +7445,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9702</t>
+          <t>7867</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>73131</t>
+          <t>72843</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26327</t>
+          <t>27014</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>45861</t>
+          <t>45195</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7495,12 +7495,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>27508</t>
+          <t>27585</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>111794</t>
+          <t>112111</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>15,11%</t>
         </is>
       </c>
     </row>
@@ -7558,12 +7558,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>25587</t>
+          <t>22643</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>154558</t>
+          <t>157906</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>30,86%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>48814</t>
+          <t>48152</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>71944</t>
+          <t>70326</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7608,12 +7608,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>30,54%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>56324</t>
+          <t>61013</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>212661</t>
+          <t>213046</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>28,72%</t>
         </is>
       </c>
     </row>
@@ -7671,12 +7671,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8959</t>
+          <t>9588</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>70295</t>
+          <t>71717</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7686,12 +7686,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7706,12 +7706,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26223</t>
+          <t>25211</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>44505</t>
+          <t>42675</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7721,12 +7721,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>26874</t>
+          <t>28294</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>111208</t>
+          <t>108313</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>14,6%</t>
         </is>
       </c>
     </row>
@@ -7784,12 +7784,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6776</t>
+          <t>5780</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>53419</t>
+          <t>55683</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7799,12 +7799,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7819,12 +7819,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>13054</t>
+          <t>13533</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>29123</t>
+          <t>29582</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7834,12 +7834,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>18355</t>
+          <t>19420</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>74541</t>
+          <t>74731</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,07%</t>
         </is>
       </c>
     </row>
@@ -8014,12 +8014,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>34152</t>
+          <t>35161</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>58982</t>
+          <t>58903</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8029,12 +8029,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>28,08%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>47,1%</t>
+          <t>47,04%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>23260</t>
+          <t>22760</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>39550</t>
+          <t>39744</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,72%</t>
+          <t>37,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>61869</t>
+          <t>59687</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>91076</t>
+          <t>91413</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>39,59%</t>
+          <t>39,73%</t>
         </is>
       </c>
     </row>
@@ -8127,12 +8127,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9983</t>
+          <t>10224</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25640</t>
+          <t>25848</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8142,12 +8142,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8162,12 +8162,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11375</t>
+          <t>11724</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>24743</t>
+          <t>25233</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8177,12 +8177,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>25264</t>
+          <t>24674</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>45358</t>
+          <t>46665</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>20,28%</t>
         </is>
       </c>
     </row>
@@ -8240,12 +8240,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>23732</t>
+          <t>24389</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>45556</t>
+          <t>45383</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8255,12 +8255,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>36,24%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8275,12 +8275,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>21704</t>
+          <t>21766</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>37851</t>
+          <t>37653</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8290,12 +8290,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>36,1%</t>
+          <t>35,91%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>49875</t>
+          <t>51801</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>77106</t>
+          <t>79423</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>34,52%</t>
         </is>
       </c>
     </row>
@@ -8353,12 +8353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8514</t>
+          <t>8586</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>27077</t>
+          <t>27622</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8388,12 +8388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5565</t>
+          <t>5801</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>16720</t>
+          <t>19012</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8403,12 +8403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>17365</t>
+          <t>17065</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>38435</t>
+          <t>37765</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8438,12 +8438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,41%</t>
         </is>
       </c>
     </row>
@@ -8466,12 +8466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7497</t>
+          <t>6695</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>24927</t>
+          <t>24651</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8481,12 +8481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8501,12 +8501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>10886</t>
+          <t>10828</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>26325</t>
+          <t>25686</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8516,12 +8516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>22054</t>
+          <t>21549</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>44163</t>
+          <t>45018</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>19,57%</t>
         </is>
       </c>
     </row>
@@ -8696,12 +8696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>225188</t>
+          <t>228995</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>551880</t>
+          <t>557710</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8711,12 +8711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>82,39%</t>
+          <t>83,27%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>102752</t>
+          <t>102048</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>133244</t>
+          <t>132418</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8746,12 +8746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>37,48%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>342561</t>
+          <t>345480</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>747414</t>
+          <t>779411</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>33,77%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>73,05%</t>
+          <t>76,18%</t>
         </is>
       </c>
     </row>
@@ -8809,12 +8809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>21330</t>
+          <t>23919</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>108360</t>
+          <t>108217</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8824,12 +8824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>45612</t>
+          <t>46340</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>69276</t>
+          <t>69935</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8859,12 +8859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>60614</t>
+          <t>55472</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>167746</t>
+          <t>166324</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8894,12 +8894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,26%</t>
         </is>
       </c>
     </row>
@@ -8922,12 +8922,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>46116</t>
+          <t>45790</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>192206</t>
+          <t>190875</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8937,12 +8937,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>79693</t>
+          <t>79729</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>108134</t>
+          <t>108060</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>30,58%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>113282</t>
+          <t>101294</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>285639</t>
+          <t>285653</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9007,7 +9007,7 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -9035,12 +9035,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>18173</t>
+          <t>19052</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>91304</t>
+          <t>89262</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9050,12 +9050,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9070,12 +9070,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>36545</t>
+          <t>35998</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>58537</t>
+          <t>57825</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9085,12 +9085,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9105,12 +9105,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>45402</t>
+          <t>43800</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>137701</t>
+          <t>137752</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9120,7 +9120,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -9148,12 +9148,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>12462</t>
+          <t>13154</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>72815</t>
+          <t>73579</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9183,12 +9183,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>29004</t>
+          <t>28646</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>51039</t>
+          <t>50779</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9218,12 +9218,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>36852</t>
+          <t>35141</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>113372</t>
+          <t>112085</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>10,96%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P6704-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P6704-Estudios-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>29132</t>
+          <t>29016</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>51646</t>
+          <t>51807</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>40132</t>
+          <t>39903</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>64567</t>
+          <t>63750</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>46,48%</t>
+          <t>45,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>74227</t>
+          <t>73711</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>107278</t>
+          <t>107162</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>33,18%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27140</t>
+          <t>27689</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>48639</t>
+          <t>49631</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17880</t>
+          <t>17792</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>37285</t>
+          <t>37295</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>51217</t>
+          <t>51179</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>80475</t>
+          <t>81559</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>25,26%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>44704</t>
+          <t>44189</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>71821</t>
+          <t>69482</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>39,03%</t>
+          <t>37,76%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>24141</t>
+          <t>25302</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>44734</t>
+          <t>45596</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>32,82%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>73446</t>
+          <t>74843</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>106914</t>
+          <t>108762</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>33,68%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12791</t>
+          <t>12869</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30764</t>
+          <t>30427</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3104</t>
+          <t>3074</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14474</t>
+          <t>13529</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>19368</t>
+          <t>19299</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>40781</t>
+          <t>41155</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,74%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>21393</t>
+          <t>20813</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>41375</t>
+          <t>42359</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>12062</t>
+          <t>11379</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>29486</t>
+          <t>29154</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>37963</t>
+          <t>37054</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>64745</t>
+          <t>64380</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>19,94%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>160468</t>
+          <t>162503</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>211675</t>
+          <t>215378</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>111347</t>
+          <t>111337</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>152418</t>
+          <t>151413</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>284668</t>
+          <t>285361</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>349662</t>
+          <t>349540</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>23,58%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>128485</t>
+          <t>128566</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>178291</t>
+          <t>175765</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>85648</t>
+          <t>86720</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>124706</t>
+          <t>123189</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>228161</t>
+          <t>226891</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>288228</t>
+          <t>289449</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,53%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>253371</t>
+          <t>252740</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>310425</t>
+          <t>310176</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>34,02%</t>
+          <t>33,99%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>137721</t>
+          <t>138708</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>182350</t>
+          <t>183849</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>32,01%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>406608</t>
+          <t>406750</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>475716</t>
+          <t>478448</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>32,28%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>132223</t>
+          <t>133064</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>180487</t>
+          <t>178771</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>78675</t>
+          <t>80010</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>114856</t>
+          <t>117188</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>224093</t>
+          <t>222899</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>284259</t>
+          <t>281864</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>19,02%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>114944</t>
+          <t>114534</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>159184</t>
+          <t>159038</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>60669</t>
+          <t>62466</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>95880</t>
+          <t>95989</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>188701</t>
+          <t>186631</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>245426</t>
+          <t>245070</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,54%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>29349</t>
+          <t>29176</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>53773</t>
+          <t>54618</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>29506</t>
+          <t>28047</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>53206</t>
+          <t>51865</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>61944</t>
+          <t>63646</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>99631</t>
+          <t>98655</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>18,0%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>52793</t>
+          <t>52642</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>88954</t>
+          <t>84834</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>22589</t>
+          <t>22964</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>45554</t>
+          <t>45365</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>83035</t>
+          <t>81311</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>120681</t>
+          <t>122413</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>22,33%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>85088</t>
+          <t>84504</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>118614</t>
+          <t>119569</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>37,63%</t>
+          <t>37,93%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>63417</t>
+          <t>63427</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>95545</t>
+          <t>94140</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>41,02%</t>
+          <t>40,42%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>158968</t>
+          <t>158422</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>204126</t>
+          <t>205813</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>37,24%</t>
+          <t>37,55%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>39307</t>
+          <t>39761</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>66776</t>
+          <t>65638</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>33614</t>
+          <t>34194</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>60073</t>
+          <t>59783</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>76425</t>
+          <t>79943</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>115504</t>
+          <t>114457</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>20,88%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>42302</t>
+          <t>39003</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>71340</t>
+          <t>70458</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>23976</t>
+          <t>24944</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>48087</t>
+          <t>48144</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>72346</t>
+          <t>72627</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>109516</t>
+          <t>111085</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>20,27%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>234609</t>
+          <t>235791</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>296220</t>
+          <t>297165</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>193392</t>
+          <t>195753</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>249772</t>
+          <t>248388</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>444716</t>
+          <t>445093</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>527364</t>
+          <t>526179</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,36%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>229723</t>
+          <t>230069</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>289062</t>
+          <t>289020</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>139114</t>
+          <t>141291</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>188696</t>
+          <t>187630</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>383966</t>
+          <t>385786</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>458496</t>
+          <t>462891</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,67%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>405735</t>
+          <t>405697</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>475521</t>
+          <t>474572</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>33,68%</t>
+          <t>33,62%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>244209</t>
+          <t>243910</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>304854</t>
+          <t>301030</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>25,91%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>667577</t>
+          <t>665493</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>755178</t>
+          <t>755457</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>32,09%</t>
+          <t>32,1%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>201774</t>
+          <t>197318</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>257875</t>
+          <t>255943</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>126849</t>
+          <t>129151</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>175628</t>
+          <t>174145</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>343964</t>
+          <t>341170</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>418897</t>
+          <t>413552</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>17,57%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>194241</t>
+          <t>193264</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>250960</t>
+          <t>250747</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>110859</t>
+          <t>110232</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>153483</t>
+          <t>156304</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>318779</t>
+          <t>322559</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>394345</t>
+          <t>392910</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,7%</t>
         </is>
       </c>
     </row>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>26641</t>
+          <t>26718</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>47572</t>
+          <t>47728</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>33,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12069</t>
+          <t>11797</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26688</t>
+          <t>27164</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>37,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>43593</t>
+          <t>44227</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>67567</t>
+          <t>68353</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>31,76%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18125</t>
+          <t>18532</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>36507</t>
+          <t>36867</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8331</t>
+          <t>8836</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22258</t>
+          <t>21280</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>29,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>29228</t>
+          <t>29686</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>52585</t>
+          <t>53146</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,7%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>39221</t>
+          <t>38657</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>62928</t>
+          <t>62856</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>27,01%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>43,97%</t>
+          <t>43,92%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>15170</t>
+          <t>15101</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>29865</t>
+          <t>30380</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>41,43%</t>
+          <t>42,14%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>59972</t>
+          <t>59086</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>86354</t>
+          <t>88129</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>40,13%</t>
+          <t>40,95%</t>
         </is>
       </c>
     </row>
@@ -4030,12 +4030,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11969</t>
+          <t>11344</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28714</t>
+          <t>29402</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4045,12 +4045,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4059</t>
+          <t>4890</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16124</t>
+          <t>16005</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>20547</t>
+          <t>19247</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>40406</t>
+          <t>41160</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4115,12 +4115,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>19,13%</t>
         </is>
       </c>
     </row>
@@ -4143,12 +4143,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4972</t>
+          <t>4963</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>17750</t>
+          <t>17884</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4163,7 +4163,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3806</t>
+          <t>3903</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>14296</t>
+          <t>14428</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>11713</t>
+          <t>11857</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>27629</t>
+          <t>28496</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>13,24%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>196707</t>
+          <t>196679</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>249231</t>
+          <t>252513</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4393,7 +4393,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>141936</t>
+          <t>139628</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>186075</t>
+          <t>183929</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>352189</t>
+          <t>352220</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>421681</t>
+          <t>422637</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4463,7 +4463,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>26,78%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>124389</t>
+          <t>125128</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>169356</t>
+          <t>170101</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>105957</t>
+          <t>107074</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>147660</t>
+          <t>148737</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>243388</t>
+          <t>244806</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>306204</t>
+          <t>305421</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,36%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>248934</t>
+          <t>250893</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>308372</t>
+          <t>306897</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>170810</t>
+          <t>166380</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>215219</t>
+          <t>213274</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>32,67%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>431216</t>
+          <t>432174</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>506460</t>
+          <t>501604</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>31,79%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>157890</t>
+          <t>156296</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>207090</t>
+          <t>206434</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>96814</t>
+          <t>98094</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>137290</t>
+          <t>140350</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>264728</t>
+          <t>264281</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>324165</t>
+          <t>329135</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,86%</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>82362</t>
+          <t>82442</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>120603</t>
+          <t>123807</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>43298</t>
+          <t>41872</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>72079</t>
+          <t>70967</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>132930</t>
+          <t>132084</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>182287</t>
+          <t>180152</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,42%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>56982</t>
+          <t>56944</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>87679</t>
+          <t>88088</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>62506</t>
+          <t>64329</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>95115</t>
+          <t>94025</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>30,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>128015</t>
+          <t>129269</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>171776</t>
+          <t>172605</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>26,19%</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>55575</t>
+          <t>55954</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>88570</t>
+          <t>88339</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>40513</t>
+          <t>42009</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>67960</t>
+          <t>68578</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>104787</t>
+          <t>104347</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>146012</t>
+          <t>145968</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5253,7 +5253,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>83109</t>
+          <t>81858</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>116773</t>
+          <t>118329</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>33,31%</t>
+          <t>33,75%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>71216</t>
+          <t>70285</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>103246</t>
+          <t>104003</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>33,72%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>163048</t>
+          <t>163245</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>209238</t>
+          <t>208093</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>31,75%</t>
+          <t>31,57%</t>
         </is>
       </c>
     </row>
@@ -5394,12 +5394,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>44912</t>
+          <t>46356</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>75417</t>
+          <t>77934</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5409,12 +5409,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5429,12 +5429,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>41098</t>
+          <t>41189</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>68331</t>
+          <t>66982</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5444,12 +5444,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>94766</t>
+          <t>96655</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>133794</t>
+          <t>136281</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,68%</t>
         </is>
       </c>
     </row>
@@ -5507,12 +5507,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>37390</t>
+          <t>36945</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>65502</t>
+          <t>64629</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5522,12 +5522,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>25771</t>
+          <t>25350</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>49600</t>
+          <t>48682</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>68886</t>
+          <t>70567</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>104122</t>
+          <t>105016</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,93%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>300564</t>
+          <t>296707</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>367538</t>
+          <t>364413</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>234327</t>
+          <t>235858</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>289287</t>
+          <t>292402</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>547694</t>
+          <t>548201</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>634772</t>
+          <t>633628</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>25,84%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>218756</t>
+          <t>216191</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>278340</t>
+          <t>273158</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>171019</t>
+          <t>171339</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>220399</t>
+          <t>220459</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>401715</t>
+          <t>400705</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>482287</t>
+          <t>476317</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>19,42%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>388942</t>
+          <t>392385</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>461917</t>
+          <t>462117</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>27,65%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>32,57%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>270956</t>
+          <t>270127</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>326793</t>
+          <t>328939</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>31,83%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>679753</t>
+          <t>682244</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>771225</t>
+          <t>766524</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>31,26%</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>231663</t>
+          <t>230770</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>288299</t>
+          <t>290910</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6091,82 +6091,82 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
+          <t>16,26%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>20,5%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>179373</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>155783</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>203728</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>17,36%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>15,08%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>19,72%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>417</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>438501</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>400545</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>479006</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>17,88%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
           <t>16,33%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>20,32%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>173</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>179373</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>155421</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>204384</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>17,36%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>15,04%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>19,78%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>417</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>438501</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>398783</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>479309</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>17,88%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>16,26%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,53%</t>
         </is>
       </c>
     </row>
@@ -6189,12 +6189,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>137661</t>
+          <t>138010</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>185950</t>
+          <t>188672</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6204,12 +6204,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>81568</t>
+          <t>81986</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>120170</t>
+          <t>118864</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>228942</t>
+          <t>231828</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>292972</t>
+          <t>292497</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,93%</t>
         </is>
       </c>
     </row>
@@ -6645,32 +6645,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>7865</t>
+          <t>15200</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3500</t>
+          <t>7821</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13712</t>
+          <t>24538</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>36,69%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>41,62%</t>
+          <t>59,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6680,32 +6680,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>5107</t>
+          <t>5891</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2375</t>
+          <t>2943</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8558</t>
+          <t>10542</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,01%</t>
+          <t>44,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6715,32 +6715,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>12972</t>
+          <t>21091</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7985</t>
+          <t>13199</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20372</t>
+          <t>32294</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>32,42%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>39,83%</t>
+          <t>49,65%</t>
         </is>
       </c>
     </row>
@@ -6758,32 +6758,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12882</t>
+          <t>11958</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7259</t>
+          <t>5999</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19673</t>
+          <t>19455</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>39,1%</t>
+          <t>28,86%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>59,72%</t>
+          <t>46,96%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6793,32 +6793,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4150</t>
+          <t>4395</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1814</t>
+          <t>1596</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7799</t>
+          <t>8016</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>33,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6828,32 +6828,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>17032</t>
+          <t>16352</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10665</t>
+          <t>9329</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>24307</t>
+          <t>24206</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>47,53%</t>
+          <t>37,21%</t>
         </is>
       </c>
     </row>
@@ -6871,32 +6871,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>4924</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1889</t>
+          <t>1834</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10520</t>
+          <t>10126</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6906,32 +6906,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>6229</t>
+          <t>9093</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3495</t>
+          <t>5276</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9516</t>
+          <t>13447</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>38,5%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>52,27%</t>
+          <t>56,93%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6941,32 +6941,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>11230</t>
+          <t>14017</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6698</t>
+          <t>8124</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>17137</t>
+          <t>20801</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>31,98%</t>
         </is>
       </c>
     </row>
@@ -6984,32 +6984,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4270</t>
+          <t>6338</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1124</t>
+          <t>1958</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11228</t>
+          <t>16629</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>40,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7019,32 +7019,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>3494</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>603</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>7341</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7054,32 +7054,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>6289</t>
+          <t>9832</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2736</t>
+          <t>4757</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13089</t>
+          <t>18698</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>28,74%</t>
         </is>
       </c>
     </row>
@@ -7097,32 +7097,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2925</t>
+          <t>3010</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>703</t>
+          <t>775</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8534</t>
+          <t>7867</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7132,7 +7132,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>746</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -7142,12 +7142,12 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2902</t>
+          <t>3259</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -7157,7 +7157,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7167,32 +7167,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>3622</t>
+          <t>3756</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>739</t>
+          <t>1102</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>8072</t>
+          <t>9824</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,1%</t>
         </is>
       </c>
     </row>
@@ -7210,17 +7210,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>32942</t>
+          <t>41429</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>32942</t>
+          <t>41429</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>32942</t>
+          <t>41429</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7245,17 +7245,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>18203</t>
+          <t>23619</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18203</t>
+          <t>23619</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>18203</t>
+          <t>23619</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7280,17 +7280,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>51145</t>
+          <t>65048</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>51145</t>
+          <t>65048</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>51145</t>
+          <t>65048</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7327,32 +7327,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>342381</t>
+          <t>108235</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>177970</t>
+          <t>89370</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>464485</t>
+          <t>130685</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>66,92%</t>
+          <t>36,62%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>34,78%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>44,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7362,32 +7362,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>81693</t>
+          <t>91220</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>69769</t>
+          <t>78573</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>97113</t>
+          <t>104446</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>35,48%</t>
+          <t>35,68%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>30,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>42,17%</t>
+          <t>40,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7397,32 +7397,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>424074</t>
+          <t>199456</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>255809</t>
+          <t>178774</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>601979</t>
+          <t>226111</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>57,16%</t>
+          <t>36,18%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>32,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>81,14%</t>
+          <t>41,02%</t>
         </is>
       </c>
     </row>
@@ -7440,32 +7440,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>34258</t>
+          <t>38275</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7867</t>
+          <t>27666</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>72843</t>
+          <t>50921</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7475,67 +7475,67 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>35556</t>
+          <t>40450</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>27014</t>
+          <t>31599</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>45195</t>
+          <t>52040</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
+          <t>12,36%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>20,35%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>78725</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>64646</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>96493</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>14,28%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
           <t>11,73%</t>
         </is>
       </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>19,63%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>69814</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>27585</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>112111</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>9,41%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>3,72%</t>
-        </is>
-      </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>17,5%</t>
         </is>
       </c>
     </row>
@@ -7553,32 +7553,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>76906</t>
+          <t>83108</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>22643</t>
+          <t>65660</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>157906</t>
+          <t>101424</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>28,12%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>34,32%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7588,32 +7588,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>58600</t>
+          <t>62820</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>48152</t>
+          <t>51016</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>70326</t>
+          <t>76089</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>29,76%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7623,32 +7623,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>135505</t>
+          <t>145928</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>61013</t>
+          <t>125195</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>213046</t>
+          <t>167335</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>30,36%</t>
         </is>
       </c>
     </row>
@@ -7666,32 +7666,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>33215</t>
+          <t>39885</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9588</t>
+          <t>27331</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>71717</t>
+          <t>58128</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7701,32 +7701,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>34068</t>
+          <t>36743</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25211</t>
+          <t>27215</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>42675</t>
+          <t>47754</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7736,32 +7736,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>67283</t>
+          <t>76628</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>28294</t>
+          <t>61064</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>108313</t>
+          <t>93646</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>16,99%</t>
         </is>
       </c>
     </row>
@@ -7779,32 +7779,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>24882</t>
+          <t>26030</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5780</t>
+          <t>16052</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>55683</t>
+          <t>37844</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7814,32 +7814,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>20358</t>
+          <t>24464</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>13533</t>
+          <t>16952</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>29582</t>
+          <t>35028</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7849,32 +7849,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>45239</t>
+          <t>50495</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>19420</t>
+          <t>37257</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>74731</t>
+          <t>66146</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>12,0%</t>
         </is>
       </c>
     </row>
@@ -7892,17 +7892,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>511641</t>
+          <t>295534</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>511641</t>
+          <t>295534</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>511641</t>
+          <t>295534</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7927,17 +7927,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>230274</t>
+          <t>255697</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>230274</t>
+          <t>255697</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>230274</t>
+          <t>255697</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7962,17 +7962,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>741915</t>
+          <t>551231</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>741915</t>
+          <t>551231</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>741915</t>
+          <t>551231</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8009,32 +8009,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>45894</t>
+          <t>49164</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>35161</t>
+          <t>37337</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>58903</t>
+          <t>64135</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>36,65%</t>
+          <t>35,13%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>47,04%</t>
+          <t>45,83%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8044,32 +8044,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>30462</t>
+          <t>33404</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>22760</t>
+          <t>24406</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>39744</t>
+          <t>43521</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>38,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8079,32 +8079,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>76356</t>
+          <t>82568</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>59687</t>
+          <t>68328</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>91413</t>
+          <t>98499</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>32,47%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>39,73%</t>
+          <t>38,74%</t>
         </is>
       </c>
     </row>
@@ -8122,32 +8122,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>16829</t>
+          <t>18961</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10224</t>
+          <t>11729</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25848</t>
+          <t>29608</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8157,27 +8157,27 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>17317</t>
+          <t>19119</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11724</t>
+          <t>13371</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>25233</t>
+          <t>27517</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -8192,32 +8192,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>34145</t>
+          <t>38080</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>24674</t>
+          <t>27675</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>46665</t>
+          <t>50027</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>19,68%</t>
         </is>
       </c>
     </row>
@@ -8235,32 +8235,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>34024</t>
+          <t>38783</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>24389</t>
+          <t>27897</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>45383</t>
+          <t>50667</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>36,24%</t>
+          <t>36,21%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8270,32 +8270,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>29091</t>
+          <t>32340</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>21766</t>
+          <t>23043</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>37653</t>
+          <t>42081</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>36,81%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8305,32 +8305,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>63115</t>
+          <t>71124</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>51801</t>
+          <t>56727</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>79423</t>
+          <t>85959</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>34,52%</t>
+          <t>33,81%</t>
         </is>
       </c>
     </row>
@@ -8348,32 +8348,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>15100</t>
+          <t>16821</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8586</t>
+          <t>9284</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>27622</t>
+          <t>29863</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8383,32 +8383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>10354</t>
+          <t>11594</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5801</t>
+          <t>6786</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>19012</t>
+          <t>18995</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8418,32 +8418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>25455</t>
+          <t>28416</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>17065</t>
+          <t>18557</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>37765</t>
+          <t>41754</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,42%</t>
         </is>
       </c>
     </row>
@@ -8461,32 +8461,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>13368</t>
+          <t>16211</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6695</t>
+          <t>8149</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>24651</t>
+          <t>29883</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8496,32 +8496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>17626</t>
+          <t>17869</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>10828</t>
+          <t>10578</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>25686</t>
+          <t>26317</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8531,32 +8531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>30994</t>
+          <t>34080</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>21549</t>
+          <t>24248</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>45018</t>
+          <t>50529</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,87%</t>
         </is>
       </c>
     </row>
@@ -8574,17 +8574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>125215</t>
+          <t>139941</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>125215</t>
+          <t>139941</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>125215</t>
+          <t>139941</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8609,17 +8609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>104849</t>
+          <t>114326</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>104849</t>
+          <t>114326</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>104849</t>
+          <t>114326</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8644,17 +8644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>230064</t>
+          <t>254267</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>230064</t>
+          <t>254267</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>230064</t>
+          <t>254267</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8691,32 +8691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>396140</t>
+          <t>172599</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>228995</t>
+          <t>148930</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>557710</t>
+          <t>198106</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>59,14%</t>
+          <t>36,19%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>34,19%</t>
+          <t>31,23%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>83,27%</t>
+          <t>41,54%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8726,32 +8726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>117261</t>
+          <t>130515</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>102048</t>
+          <t>113720</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>132418</t>
+          <t>148555</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>33,16%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>28,89%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>37,48%</t>
+          <t>37,74%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8761,32 +8761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>513401</t>
+          <t>303114</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>345480</t>
+          <t>272272</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>779411</t>
+          <t>334294</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>50,18%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>76,18%</t>
+          <t>38,4%</t>
         </is>
       </c>
     </row>
@@ -8804,32 +8804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>63968</t>
+          <t>69194</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>23919</t>
+          <t>55429</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>108217</t>
+          <t>88669</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8839,32 +8839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>57023</t>
+          <t>63964</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>46340</t>
+          <t>51996</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>69935</t>
+          <t>77476</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8874,32 +8874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>120991</t>
+          <t>133157</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>55472</t>
+          <t>111151</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>166324</t>
+          <t>154786</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>17,78%</t>
         </is>
       </c>
     </row>
@@ -8917,32 +8917,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>115931</t>
+          <t>126816</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>45790</t>
+          <t>106548</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>190875</t>
+          <t>151653</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>31,8%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8952,32 +8952,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>93919</t>
+          <t>104252</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>79729</t>
+          <t>90381</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>108060</t>
+          <t>122875</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>26,48%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8987,32 +8987,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>209850</t>
+          <t>231068</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>101294</t>
+          <t>206391</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>285653</t>
+          <t>262227</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>30,12%</t>
         </is>
       </c>
     </row>
@@ -9030,32 +9030,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>52585</t>
+          <t>63044</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>19052</t>
+          <t>45597</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>89262</t>
+          <t>84669</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9065,32 +9065,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>46442</t>
+          <t>51832</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>35998</t>
+          <t>41348</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>57825</t>
+          <t>66910</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9100,32 +9100,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>99027</t>
+          <t>114876</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>43800</t>
+          <t>95707</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>137752</t>
+          <t>136609</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>15,69%</t>
         </is>
       </c>
     </row>
@@ -9143,32 +9143,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>41175</t>
+          <t>45251</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>13154</t>
+          <t>32113</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>73579</t>
+          <t>64286</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9178,32 +9178,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>38680</t>
+          <t>43079</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>28646</t>
+          <t>32252</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>50779</t>
+          <t>55962</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9213,32 +9213,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>79855</t>
+          <t>88330</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>35141</t>
+          <t>69487</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>112085</t>
+          <t>110376</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>12,68%</t>
         </is>
       </c>
     </row>
@@ -9256,17 +9256,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>669799</t>
+          <t>476904</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>669799</t>
+          <t>476904</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>669799</t>
+          <t>476904</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9291,17 +9291,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>353325</t>
+          <t>393642</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>353325</t>
+          <t>393642</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>353325</t>
+          <t>393642</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9326,17 +9326,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1023124</t>
+          <t>870546</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1023124</t>
+          <t>870546</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1023124</t>
+          <t>870546</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
